--- a/Task1_Global_Fossil_Fuel_Market_Value.xlsx
+++ b/Task1_Global_Fossil_Fuel_Market_Value.xlsx
@@ -475,7 +475,7 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -740,20 +740,20 @@
         <v>1020</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Coal India notified avg</t>
+          <t>CIL blended all-in (incl. levies)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Mine-gate</t>
+          <t>Mine-gate + levies</t>
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>20400</v>
+        <v>30600</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>2024</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>CIL FSA ~Rs 1450/t; FY24-25; IEA 1,089 Mt (incl. met)</t>
+          <t>CIL FSA Rs1514 + royalty 14% + DMF + NMET + GST 5% + cess Rs400 = ~Rs2270/t ($27); e-auction ~Rs3490/t ($42); blended ~$30/t</t>
         </is>
       </c>
     </row>
@@ -794,20 +794,20 @@
         <v>28</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>242</v>
+        <v>280</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>PLV HCC import parity</t>
+          <t>PLV HCC import parity + duties</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>CIF</t>
+          <t>CIF + duties</t>
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6776</v>
+        <v>7840</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>2024</v>
@@ -819,7 +819,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Small domestic met coal; mostly imported</t>
+          <t>Imported met coal CIF ~$242 + 2.5% customs + GST + cess; domestic met at import parity</t>
         </is>
       </c>
     </row>
